--- a/test-files/маркетинг.xlsx
+++ b/test-files/маркетинг.xlsx
@@ -58,7 +58,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,14 +425,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,62 +465,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Иванов Иван Иванович</t>
+          <t>Кузнецов Дмитрий Сергеевич</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Разработчик</t>
+          <t>Менеджер</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Разработка</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>108513</v>
+        <v>75623.78999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.07.2019</t>
+          <t>12.02.2024</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Кузнецов Дмитрий Сергеевич</t>
+          <t>Сидоров Алексей Николаевич</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HR-специалист</t>
+          <t>Бухгалтер</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Поддержка</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>192964</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>23.12.2018</t>
-        </is>
-      </c>
+          <t>Аналитика</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Козлова Юлия Романовна</t>
+          <t>Лебедев Сергей Александрович</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Дизайнер</t>
+          <t>UX-исследователь</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -529,23 +523,23 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>57811</v>
+        <v>233848</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.01.2019</t>
+          <t>21.06.2020</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Попов Андрей Дмитриевич</t>
+          <t>Сидорова Ольга Дмитриевна</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Старший аналитик</t>
+          <t>Бухгалтер</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,63 +548,278 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>207815</v>
+        <v>251454.81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.04.2018</t>
+          <t>25.10.2021</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Лебедева Светлана Петровна</t>
+          <t>Козлов Артём Олегович</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Старший аналитик</t>
+          <t>Аналитик</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Поддержка</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>220363</v>
+        <v>74312</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.02.2024</t>
+          <t>10.01.2022</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Кузнецова Екатерина Игоревна</t>
+          <t>Волков Антон Игоревич</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Старший аналитик</t>
+          <t>Бухгалтер</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>190568</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>31.03.2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Сидоров Алексей Николаевич</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UX-исследователь</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>275891</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>27.02.2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Морозова Анастасия Олеговна</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Старший менеджер</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Маркетинг</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>70916</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>18.02.2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Иванова Анна Сергеевна</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Разработчик</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Дизайн</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>147040</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>29.12.2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Морозова Анастасия Олеговна</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Руководитель отдела</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Разработка</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>232281.7</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>04.04.2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Козлов Артём Олегович</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Руководитель отдела</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Продажи</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>204472</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>13.02.2021</t>
-        </is>
-      </c>
+      <c r="D12" t="n">
+        <v>253423</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Петров Пётр Петрович</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Специалист по продажам</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Поддержка</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>278284.03</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>12.07.2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Попов Андрей Дмитриевич</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Финансовый аналитик</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Дизайн</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>170285</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>26.07.2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Лебедев Сергей Александрович</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Тестировщик</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>202969</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>17.06.2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Смирнов Владимир Андреевич</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>UX-исследователь</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Дизайн</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
